--- a/VerveStacks_BIH_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F3C1C72-ACB6-4A2E-B691-9510CD880506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{109FC68E-77AD-49F3-B0BB-034D0A38FABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,13 +753,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S02aH13,S04aH05,S04aH08,S01aH03,S02aH10,S05aH03,S05aH06,S01aH11,S04aH10,S06aH06,S06aH10,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S03aH03,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S02aH14,S03aH11,S04aH03,S05aH13,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S04aH04,S05aH10</t>
+    <t>S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH14,S04aH14,S05aH08,S06aH13,S02aH13,S04aH05,S04aH08,S01aH10,S02aH11,S04aH12,S01aH11,S04aH10,S06aH06,S06aH10,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH03,S02aH10,S05aH03,S05aH06,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S05aH11,S04aH04,S05aH10,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S03aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S06aH18,S03aH15,S03aH18,S04aH17,S05aH15,S01aH15,S03aH01,S05aH16,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S05aH17,S01aH18,S02aH02,S02aH16,S03aH17,S01aH01,S04aH01,S06aH02,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH02,S04aH18,S02aH15,S04aH15,S01aH02,S05aH01,S06aH15,S06aH16,S02aH17</t>
+    <t>S01aH01,S04aH01,S06aH02,S06aH18,S01aH16,S06aH01,S03aH15,S03aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH15,S03aH01,S05aH16,S01aH02,S05aH01,S06aH15,S06aH16,S04aH17,S05aH15,S05aH17,S02aH15,S04aH15,S03aH02,S04aH18,S02aH17,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S02aH02,S02aH16,S03aH17</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S06aH18,S03aH15,S03aH18,S04aH17,S05aH15,S01aH15,S03aH01,S05aH16,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S05aH17,S01aH18,S02aH02,S02aH16,S03aH17,S01aH01,S04aH01,S06aH02,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH02,S04aH18,S02aH15,S04aH15,S01aH02,S05aH01,S06aH15,S06aH16,S02aH17</v>
+        <v>S01aH01,S04aH01,S06aH02,S06aH18,S01aH16,S06aH01,S03aH15,S03aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH15,S03aH01,S05aH16,S01aH02,S05aH01,S06aH15,S06aH16,S04aH17,S05aH15,S05aH17,S02aH15,S04aH15,S03aH02,S04aH18,S02aH17,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S02aH02,S02aH16,S03aH17</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S02aH13,S04aH05,S04aH08,S01aH03,S02aH10,S05aH03,S05aH06,S01aH11,S04aH10,S06aH06,S06aH10,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S03aH03,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S02aH14,S03aH11,S04aH03,S05aH13,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S04aH04,S05aH10</v>
+        <v>S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH14,S04aH14,S05aH08,S06aH13,S02aH13,S04aH05,S04aH08,S01aH10,S02aH11,S04aH12,S01aH11,S04aH10,S06aH06,S06aH10,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH03,S02aH10,S05aH03,S05aH06,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S05aH11,S04aH04,S05aH10,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S03aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1482,7 +1482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3393-F06E-4E1D-9B66-2C539A01B20F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA887E6-AE97-4C5B-BDF9-634BB118DBBB}">
   <dimension ref="A9:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1690,7 +1690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3841659-11CD-449F-9DF6-578B138F862C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BE7679-3A49-476E-855C-211234046EA0}">
   <dimension ref="B9:J1522"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35864,7 +35864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5114FD-AB9A-428A-A7CD-44221F6CC274}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED1749B-A3A1-4700-9573-5AFCC208D3A6}">
   <dimension ref="B9:QF34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -54651,7 +54651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F6BE0E-64B5-49E0-A4BE-8ABF7BBC1E90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1375410A-09E1-46B4-B846-78D5FC2C91C9}">
   <dimension ref="A9:S226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -54934,7 +54934,7 @@
         <v>6.735159817351598E-3</v>
       </c>
       <c r="D16">
-        <v>8.5271279284654718E-3</v>
+        <v>8.5271279284654736E-3</v>
       </c>
       <c r="E16" t="s">
         <v>75</v>
@@ -55139,7 +55139,7 @@
         <v>6.735159817351598E-3</v>
       </c>
       <c r="D21">
-        <v>8.8791653200076277E-3</v>
+        <v>8.8791653200076242E-3</v>
       </c>
       <c r="E21" t="s">
         <v>80</v>
@@ -55583,7 +55583,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D33">
-        <v>8.8970655263572295E-3</v>
+        <v>8.8970655263572278E-3</v>
       </c>
       <c r="E33" t="s">
         <v>92</v>
@@ -55612,7 +55612,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D34">
-        <v>8.81618311248125E-3</v>
+        <v>8.8161831124812517E-3</v>
       </c>
       <c r="E34" t="s">
         <v>93</v>
@@ -55757,7 +55757,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D39">
-        <v>9.1801539749231421E-3</v>
+        <v>9.1801539749231387E-3</v>
       </c>
       <c r="E39" t="s">
         <v>98</v>
@@ -56105,7 +56105,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D51">
-        <v>8.8970655263572295E-3</v>
+        <v>8.8970655263572278E-3</v>
       </c>
       <c r="E51" t="s">
         <v>110</v>
@@ -56134,7 +56134,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D52">
-        <v>8.81618311248125E-3</v>
+        <v>8.8161831124812517E-3</v>
       </c>
       <c r="E52" t="s">
         <v>111</v>
@@ -56279,7 +56279,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D57">
-        <v>9.1801539749231421E-3</v>
+        <v>9.1801539749231387E-3</v>
       </c>
       <c r="E57" t="s">
         <v>116</v>
@@ -56656,7 +56656,7 @@
         <v>7.0776255707762558E-3</v>
       </c>
       <c r="D70">
-        <v>8.9607107044891391E-3</v>
+        <v>8.9607107044891408E-3</v>
       </c>
       <c r="E70" t="s">
         <v>129</v>
@@ -56801,7 +56801,7 @@
         <v>7.0776255707762558E-3</v>
       </c>
       <c r="D75">
-        <v>9.3306483023808985E-3</v>
+        <v>9.330648302380895E-3</v>
       </c>
       <c r="E75" t="s">
         <v>134</v>
@@ -57149,7 +57149,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D87">
-        <v>8.8970655263572295E-3</v>
+        <v>8.8970655263572278E-3</v>
       </c>
       <c r="E87" t="s">
         <v>146</v>
@@ -57178,7 +57178,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D88">
-        <v>8.81618311248125E-3</v>
+        <v>8.8161831124812517E-3</v>
       </c>
       <c r="E88" t="s">
         <v>147</v>
@@ -57323,7 +57323,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D93">
-        <v>9.1801539749231421E-3</v>
+        <v>9.1801539749231387E-3</v>
       </c>
       <c r="E93" t="s">
         <v>152</v>
@@ -57671,7 +57671,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D105">
-        <v>8.8970655263572295E-3</v>
+        <v>8.8970655263572278E-3</v>
       </c>
       <c r="E105" t="s">
         <v>164</v>
@@ -57700,7 +57700,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D106">
-        <v>8.81618311248125E-3</v>
+        <v>8.8161831124812517E-3</v>
       </c>
       <c r="E106" t="s">
         <v>165</v>
@@ -57845,7 +57845,7 @@
         <v>6.9634703196347035E-3</v>
       </c>
       <c r="D111">
-        <v>9.1801539749231421E-3</v>
+        <v>9.1801539749231387E-3</v>
       </c>
       <c r="E111" t="s">
         <v>170</v>
